--- a/ig/nr-prepare-release/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
+++ b/ig/nr-prepare-release/StructureDefinition-as-ext-codeableconcept-timed-metadata.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T13:03:45+00:00</t>
+    <t>2024-02-07T13:05:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
